--- a/CLIENTES POR CANAL.xlsx
+++ b/CLIENTES POR CANAL.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\estadistica\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\APP BI SEDISUR\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -673,127 +673,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="13">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1083,1029 +963,1026 @@
   <dimension ref="A1:C92"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.88671875" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.88671875" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="41.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24" style="4" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="11.5546875" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="B1" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>147</v>
-      </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>106</v>
-      </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>103</v>
-      </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="B4" s="3" t="s">
+      <c r="A4" s="3" t="s">
         <v>102</v>
       </c>
+      <c r="B4" s="2" t="s">
+        <v>101</v>
+      </c>
       <c r="C4" s="2" t="s">
-        <v>101</v>
+        <v>189</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="B5" s="3" t="s">
+      <c r="A5" s="3" t="s">
         <v>100</v>
       </c>
+      <c r="B5" s="2" t="s">
+        <v>99</v>
+      </c>
       <c r="C5" s="2" t="s">
-        <v>99</v>
+        <v>189</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="B6" s="3" t="s">
+      <c r="A6" s="3" t="s">
         <v>98</v>
       </c>
+      <c r="B6" s="2" t="s">
+        <v>97</v>
+      </c>
       <c r="C6" s="2" t="s">
-        <v>97</v>
+        <v>189</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="B7" s="3" t="s">
+      <c r="A7" s="3" t="s">
         <v>151</v>
       </c>
+      <c r="B7" s="2" t="s">
+        <v>96</v>
+      </c>
       <c r="C7" s="2" t="s">
-        <v>96</v>
+        <v>189</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="B8" s="3" t="s">
+      <c r="A8" s="3" t="s">
         <v>95</v>
       </c>
+      <c r="B8" s="2" t="s">
+        <v>94</v>
+      </c>
       <c r="C8" s="2" t="s">
-        <v>94</v>
+        <v>189</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="B9" s="3" t="s">
+      <c r="A9" s="3" t="s">
         <v>93</v>
       </c>
+      <c r="B9" s="2" t="s">
+        <v>92</v>
+      </c>
       <c r="C9" s="2" t="s">
-        <v>92</v>
+        <v>189</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="B10" s="3" t="s">
+      <c r="A10" s="3" t="s">
         <v>91</v>
       </c>
+      <c r="B10" s="2" t="s">
+        <v>90</v>
+      </c>
       <c r="C10" s="2" t="s">
-        <v>90</v>
+        <v>189</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="B11" s="3" t="s">
+      <c r="A11" s="3" t="s">
         <v>89</v>
       </c>
+      <c r="B11" s="2" t="s">
+        <v>88</v>
+      </c>
       <c r="C11" s="2" t="s">
-        <v>88</v>
+        <v>189</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="B12" s="3" t="s">
+      <c r="A12" s="3" t="s">
         <v>87</v>
       </c>
+      <c r="B12" s="2" t="s">
+        <v>86</v>
+      </c>
       <c r="C12" s="2" t="s">
-        <v>86</v>
+        <v>189</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
-        <v>189</v>
+      <c r="A13" s="1" t="s">
+        <v>171</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="C13" s="1" t="s">
         <v>172</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="B16" s="3" t="s">
+      <c r="A16" s="3" t="s">
         <v>85</v>
       </c>
+      <c r="B16" s="2" t="s">
+        <v>84</v>
+      </c>
       <c r="C16" s="2" t="s">
-        <v>84</v>
+        <v>189</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="B17" s="3" t="s">
+      <c r="A17" s="3" t="s">
         <v>83</v>
       </c>
+      <c r="B17" s="2" t="s">
+        <v>82</v>
+      </c>
       <c r="C17" s="2" t="s">
-        <v>82</v>
+        <v>189</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="B18" s="3" t="s">
+      <c r="A18" s="3" t="s">
         <v>81</v>
       </c>
+      <c r="B18" s="2" t="s">
+        <v>80</v>
+      </c>
       <c r="C18" s="2" t="s">
-        <v>80</v>
+        <v>189</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="B19" s="3" t="s">
+      <c r="A19" s="3" t="s">
         <v>79</v>
       </c>
+      <c r="B19" s="2" t="s">
+        <v>78</v>
+      </c>
       <c r="C19" s="2" t="s">
-        <v>78</v>
+        <v>189</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="B20" s="3" t="s">
+      <c r="A20" s="3" t="s">
         <v>77</v>
       </c>
+      <c r="B20" s="2" t="s">
+        <v>76</v>
+      </c>
       <c r="C20" s="2" t="s">
-        <v>76</v>
+        <v>189</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="B21" s="3" t="s">
+      <c r="A21" s="3" t="s">
         <v>75</v>
       </c>
+      <c r="B21" s="2" t="s">
+        <v>74</v>
+      </c>
       <c r="C21" s="2" t="s">
-        <v>74</v>
+        <v>189</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="B22" s="3" t="s">
+      <c r="A22" s="3" t="s">
         <v>152</v>
       </c>
+      <c r="B22" s="2" t="s">
+        <v>165</v>
+      </c>
       <c r="C22" s="2" t="s">
-        <v>165</v>
+        <v>189</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="B23" s="3" t="s">
+      <c r="A23" s="3" t="s">
         <v>73</v>
       </c>
+      <c r="B23" s="2" t="s">
+        <v>72</v>
+      </c>
       <c r="C23" s="2" t="s">
-        <v>72</v>
+        <v>189</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="B24" s="3" t="s">
+      <c r="A24" s="3" t="s">
         <v>71</v>
       </c>
+      <c r="B24" s="2" t="s">
+        <v>70</v>
+      </c>
       <c r="C24" s="2" t="s">
-        <v>70</v>
+        <v>189</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="B25" s="3" t="s">
+      <c r="A25" s="3" t="s">
         <v>69</v>
       </c>
+      <c r="B25" s="2" t="s">
+        <v>68</v>
+      </c>
       <c r="C25" s="2" t="s">
-        <v>68</v>
+        <v>189</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A26" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="B26" s="3" t="s">
+      <c r="A26" s="3" t="s">
         <v>67</v>
       </c>
+      <c r="B26" s="2" t="s">
+        <v>66</v>
+      </c>
       <c r="C26" s="2" t="s">
-        <v>66</v>
+        <v>189</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>145</v>
-      </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>143</v>
-      </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
+      <c r="A30" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>141</v>
-      </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
+      <c r="A31" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>139</v>
-      </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A32" s="2" t="s">
+      <c r="A32" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>137</v>
-      </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" s="2" t="s">
+      <c r="A33" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C33" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>135</v>
-      </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" s="2" t="s">
+      <c r="A34" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>133</v>
-      </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" s="2" t="s">
+      <c r="A35" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C35" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
+      <c r="A36" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C36" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>129</v>
-      </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
+      <c r="A37" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C37" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>127</v>
-      </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
+      <c r="A38" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>125</v>
-      </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A39" s="2" t="s">
+      <c r="A39" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C39" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>123</v>
-      </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A40" s="2" t="s">
+      <c r="A40" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="B40" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>121</v>
-      </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A41" s="2" t="s">
+      <c r="A41" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C41" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="B41" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>119</v>
-      </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A42" s="2" t="s">
+      <c r="A42" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C42" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="B42" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>117</v>
-      </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A43" s="2" t="s">
+      <c r="A43" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C43" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="B43" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>115</v>
-      </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A44" s="2" t="s">
+      <c r="A44" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C44" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="B44" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>113</v>
-      </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A45" s="2" t="s">
+      <c r="A45" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C45" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="B45" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>111</v>
-      </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A46" s="2" t="s">
+      <c r="A46" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>150</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C47" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="B47" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>188</v>
-      </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A48" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B48" s="3" t="s">
+      <c r="A48" s="3" t="s">
         <v>65</v>
       </c>
+      <c r="B48" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="C48" s="2" t="s">
-        <v>64</v>
+        <v>170</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A49" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B49" s="3" t="s">
+      <c r="A49" s="3" t="s">
         <v>153</v>
       </c>
+      <c r="B49" s="2" t="s">
+        <v>166</v>
+      </c>
       <c r="C49" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A50" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B50" s="3" t="s">
+      <c r="A50" s="3" t="s">
         <v>63</v>
       </c>
+      <c r="B50" s="2" t="s">
+        <v>62</v>
+      </c>
       <c r="C50" s="2" t="s">
-        <v>62</v>
+        <v>170</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A51" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B51" s="3" t="s">
+      <c r="A51" s="3" t="s">
         <v>61</v>
       </c>
+      <c r="B51" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="C51" s="2" t="s">
-        <v>60</v>
+        <v>170</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A52" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B52" s="3" t="s">
+      <c r="A52" s="3" t="s">
         <v>59</v>
       </c>
+      <c r="B52" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="C52" s="2" t="s">
-        <v>58</v>
+        <v>170</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A53" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B53" s="3" t="s">
+      <c r="A53" s="3" t="s">
         <v>57</v>
       </c>
+      <c r="B53" s="2" t="s">
+        <v>56</v>
+      </c>
       <c r="C53" s="2" t="s">
-        <v>56</v>
+        <v>170</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A54" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B54" s="3" t="s">
+      <c r="A54" s="3" t="s">
         <v>55</v>
       </c>
+      <c r="B54" s="2" t="s">
+        <v>54</v>
+      </c>
       <c r="C54" s="2" t="s">
-        <v>54</v>
+        <v>170</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A55" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B55" s="3" t="s">
+      <c r="A55" s="3" t="s">
         <v>53</v>
       </c>
+      <c r="B55" s="2" t="s">
+        <v>52</v>
+      </c>
       <c r="C55" s="2" t="s">
-        <v>52</v>
+        <v>170</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A56" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B56" s="3" t="s">
+      <c r="A56" s="3" t="s">
         <v>51</v>
       </c>
+      <c r="B56" s="2" t="s">
+        <v>50</v>
+      </c>
       <c r="C56" s="2" t="s">
-        <v>50</v>
+        <v>170</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A57" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B57" s="3" t="s">
+      <c r="A57" s="3" t="s">
         <v>154</v>
       </c>
+      <c r="B57" s="2" t="s">
+        <v>167</v>
+      </c>
       <c r="C57" s="2" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A58" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B58" s="3" t="s">
+      <c r="A58" s="3" t="s">
         <v>49</v>
       </c>
+      <c r="B58" s="2" t="s">
+        <v>48</v>
+      </c>
       <c r="C58" s="2" t="s">
-        <v>48</v>
+        <v>170</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A59" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B59" s="3" t="s">
+      <c r="A59" s="3" t="s">
         <v>47</v>
       </c>
+      <c r="B59" s="2" t="s">
+        <v>46</v>
+      </c>
       <c r="C59" s="2" t="s">
-        <v>46</v>
+        <v>170</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A60" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B60" s="3" t="s">
+      <c r="A60" s="3" t="s">
         <v>155</v>
       </c>
+      <c r="B60" s="2" t="s">
+        <v>168</v>
+      </c>
       <c r="C60" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A61" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B61" s="3" t="s">
+      <c r="A61" s="3" t="s">
         <v>45</v>
       </c>
+      <c r="B61" s="2" t="s">
+        <v>44</v>
+      </c>
       <c r="C61" s="2" t="s">
-        <v>44</v>
+        <v>170</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A62" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B62" s="3" t="s">
+      <c r="A62" s="3" t="s">
         <v>43</v>
       </c>
+      <c r="B62" s="2" t="s">
+        <v>42</v>
+      </c>
       <c r="C62" s="2" t="s">
-        <v>42</v>
+        <v>170</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A63" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B63" s="3" t="s">
+      <c r="A63" s="3" t="s">
         <v>41</v>
       </c>
+      <c r="B63" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="C63" s="2" t="s">
-        <v>40</v>
+        <v>170</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A64" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B64" s="3" t="s">
+      <c r="A64" s="3" t="s">
         <v>39</v>
       </c>
+      <c r="B64" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="C64" s="2" t="s">
-        <v>38</v>
+        <v>170</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A65" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B65" s="3" t="s">
+      <c r="A65" s="3" t="s">
         <v>37</v>
       </c>
+      <c r="B65" s="2" t="s">
+        <v>36</v>
+      </c>
       <c r="C65" s="2" t="s">
-        <v>36</v>
+        <v>170</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A66" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B66" s="3" t="s">
+      <c r="A66" s="3" t="s">
         <v>35</v>
       </c>
+      <c r="B66" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="C66" s="2" t="s">
-        <v>34</v>
+        <v>170</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A67" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B67" s="3" t="s">
+      <c r="A67" s="3" t="s">
         <v>33</v>
       </c>
+      <c r="B67" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="C67" s="2" t="s">
-        <v>32</v>
+        <v>170</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A68" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B68" s="3" t="s">
+      <c r="A68" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="B68" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="C68" s="2" t="s">
-        <v>30</v>
+        <v>170</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A69" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B69" s="3" t="s">
+      <c r="A69" s="3" t="s">
         <v>29</v>
       </c>
+      <c r="B69" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="C69" s="2" t="s">
-        <v>28</v>
+        <v>170</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A70" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B70" s="3" t="s">
+      <c r="A70" s="3" t="s">
         <v>27</v>
       </c>
+      <c r="B70" s="2" t="s">
+        <v>26</v>
+      </c>
       <c r="C70" s="2" t="s">
-        <v>26</v>
+        <v>170</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A71" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B71" s="3" t="s">
+      <c r="A71" s="3" t="s">
         <v>156</v>
       </c>
+      <c r="B71" s="2" t="s">
+        <v>169</v>
+      </c>
       <c r="C71" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A72" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B72" s="3" t="s">
+      <c r="A72" s="3" t="s">
         <v>25</v>
       </c>
+      <c r="B72" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="C72" s="2" t="s">
-        <v>24</v>
+        <v>170</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A73" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B73" s="3" t="s">
+      <c r="A73" s="3" t="s">
         <v>23</v>
       </c>
+      <c r="B73" s="2" t="s">
+        <v>22</v>
+      </c>
       <c r="C73" s="2" t="s">
-        <v>22</v>
+        <v>170</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A74" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B74" s="3" t="s">
+      <c r="A74" s="3" t="s">
         <v>21</v>
       </c>
+      <c r="B74" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="C74" s="2" t="s">
-        <v>20</v>
+        <v>170</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A75" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B75" s="3" t="s">
+      <c r="A75" s="3" t="s">
         <v>19</v>
       </c>
+      <c r="B75" s="2" t="s">
+        <v>18</v>
+      </c>
       <c r="C75" s="2" t="s">
-        <v>18</v>
+        <v>170</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A76" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B76" s="3" t="s">
+      <c r="A76" s="3" t="s">
         <v>17</v>
       </c>
+      <c r="B76" s="2" t="s">
+        <v>16</v>
+      </c>
       <c r="C76" s="2" t="s">
-        <v>16</v>
+        <v>170</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A77" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B77" s="3" t="s">
+      <c r="A77" s="3" t="s">
         <v>157</v>
       </c>
+      <c r="B77" s="2" t="s">
+        <v>158</v>
+      </c>
       <c r="C77" s="2" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A78" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B78" s="3" t="s">
+      <c r="A78" s="3" t="s">
         <v>159</v>
       </c>
+      <c r="B78" s="2" t="s">
+        <v>160</v>
+      </c>
       <c r="C78" s="2" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A79" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B79" s="3" t="s">
+      <c r="A79" s="3" t="s">
         <v>161</v>
       </c>
+      <c r="B79" s="2" t="s">
+        <v>162</v>
+      </c>
       <c r="C79" s="2" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A80" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B80" s="3" t="s">
+      <c r="A80" s="3" t="s">
         <v>163</v>
       </c>
+      <c r="B80" s="2" t="s">
+        <v>164</v>
+      </c>
       <c r="C80" s="2" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A81" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B81" s="3" t="s">
+      <c r="A81" s="3" t="s">
         <v>15</v>
       </c>
+      <c r="B81" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="C81" s="2" t="s">
-        <v>14</v>
+        <v>170</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A82" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B82" s="3" t="s">
+      <c r="A82" s="3" t="s">
         <v>13</v>
       </c>
+      <c r="B82" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="C82" s="2" t="s">
-        <v>12</v>
+        <v>170</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A83" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B83" s="3" t="s">
+      <c r="A83" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="B83" s="2" t="s">
+        <v>10</v>
+      </c>
       <c r="C83" s="2" t="s">
-        <v>10</v>
+        <v>170</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A84" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B84" s="3" t="s">
+      <c r="A84" s="3" t="s">
         <v>9</v>
       </c>
+      <c r="B84" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="C84" s="2" t="s">
-        <v>8</v>
+        <v>170</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A85" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B85" s="3" t="s">
+      <c r="A85" s="3" t="s">
         <v>7</v>
       </c>
+      <c r="B85" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="C85" s="2" t="s">
-        <v>6</v>
+        <v>170</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A86" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B86" s="3" t="s">
+      <c r="A86" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="B86" s="2" t="s">
+        <v>4</v>
+      </c>
       <c r="C86" s="2" t="s">
-        <v>4</v>
+        <v>170</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A87" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B87" s="3" t="s">
+      <c r="A87" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="B87" s="2" t="s">
+        <v>2</v>
+      </c>
       <c r="C87" s="2" t="s">
-        <v>2</v>
+        <v>170</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A88" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B88" s="3" t="s">
+      <c r="A88" s="3" t="s">
         <v>1</v>
       </c>
+      <c r="B88" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="C88" s="2" t="s">
-        <v>0</v>
+        <v>170</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A91" s="2" t="s">
-        <v>170</v>
+      <c r="A91" s="1" t="s">
+        <v>173</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="C91" s="1" t="s">
         <v>174</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>186</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
-  <sortState ref="A2:C117">
-    <sortCondition ref="A2:A117"/>
-  </sortState>
-  <conditionalFormatting sqref="B1:B1048576">
+  <conditionalFormatting sqref="A1:A1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/CLIENTES POR CANAL.xlsx
+++ b/CLIENTES POR CANAL.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\APP BI SEDISUR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\estadistica\Documents\GitHub\sedisur-ventas-bi\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -658,7 +658,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -669,6 +669,9 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1102,7 +1105,7 @@
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="8" t="s">
         <v>171</v>
       </c>
       <c r="B13" s="1" t="s">
@@ -1113,7 +1116,7 @@
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="3" t="s">
         <v>177</v>
       </c>
       <c r="B14" s="2" t="s">
@@ -1124,7 +1127,7 @@
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="3" t="s">
         <v>181</v>
       </c>
       <c r="B15" s="2" t="s">
@@ -1256,7 +1259,7 @@
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="3" t="s">
         <v>175</v>
       </c>
       <c r="B27" s="2" t="s">
@@ -1476,7 +1479,7 @@
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A47" s="2" t="s">
+      <c r="A47" s="3" t="s">
         <v>187</v>
       </c>
       <c r="B47" s="2" t="s">
@@ -1938,7 +1941,7 @@
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A89" s="2" t="s">
+      <c r="A89" s="3" t="s">
         <v>183</v>
       </c>
       <c r="B89" s="2" t="s">
@@ -1949,7 +1952,7 @@
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A90" s="2" t="s">
+      <c r="A90" s="3" t="s">
         <v>179</v>
       </c>
       <c r="B90" s="2" t="s">
@@ -1960,7 +1963,7 @@
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A91" s="1" t="s">
+      <c r="A91" s="8" t="s">
         <v>173</v>
       </c>
       <c r="B91" s="1" t="s">
@@ -1971,7 +1974,7 @@
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A92" s="2" t="s">
+      <c r="A92" s="3" t="s">
         <v>185</v>
       </c>
       <c r="B92" s="2" t="s">
